--- a/salidas/empresas/GIS.xlsx
+++ b/salidas/empresas/GIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.19902992248535</v>
+        <v>12.1990327835083</v>
       </c>
       <c r="C2" t="n">
         <v>24.30500030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.35965061187744</v>
+        <v>12.35964775085449</v>
       </c>
       <c r="C3" t="n">
         <v>24.625</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.71851253509521</v>
+        <v>12.71851634979248</v>
       </c>
       <c r="C4" t="n">
         <v>25.34000015258789</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.46572875976562</v>
+        <v>12.46572589874268</v>
       </c>
       <c r="C5" t="n">
         <v>24.67000007629395</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.10998249053955</v>
+        <v>13.1099853515625</v>
       </c>
       <c r="C6" t="n">
         <v>25.94499969482422</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.05187606811523</v>
+        <v>13.05187892913818</v>
       </c>
       <c r="C7" t="n">
         <v>25.82999992370605</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.20145225524902</v>
+        <v>13.20145034790039</v>
       </c>
       <c r="C8" t="n">
         <v>25.95000076293945</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.39696025848389</v>
+        <v>14.39695930480957</v>
       </c>
       <c r="C10" t="n">
         <v>28.29999923706055</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.54366970062256</v>
+        <v>14.54367542266846</v>
       </c>
       <c r="C11" t="n">
         <v>28.40999984741211</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.32099342346191</v>
+        <v>14.32099056243896</v>
       </c>
       <c r="C12" t="n">
         <v>27.97500038146973</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.74332427978516</v>
+        <v>14.74332523345947</v>
       </c>
       <c r="C13" t="n">
         <v>28.79999923706055</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.74694728851318</v>
+        <v>14.74695491790771</v>
       </c>
       <c r="C14" t="n">
         <v>28.6200008392334</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>14.50993156433105</v>
+        <v>14.50992774963379</v>
       </c>
       <c r="C15" t="n">
         <v>28.15999984741211</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.99943256378174</v>
+        <v>14.99943447113037</v>
       </c>
       <c r="C16" t="n">
         <v>29.11000061035156</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>15.52969741821289</v>
+        <v>15.52969360351562</v>
       </c>
       <c r="C17" t="n">
         <v>29.95000076293945</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.87710857391357</v>
+        <v>15.87710475921631</v>
       </c>
       <c r="C18" t="n">
         <v>30.6200008392334</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.14599514007568</v>
+        <v>15.14598560333252</v>
       </c>
       <c r="C19" t="n">
         <v>29.20999908447266</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.51663875579834</v>
+        <v>14.51664352416992</v>
       </c>
       <c r="C20" t="n">
         <v>27.80999946594238</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.58450508117676</v>
+        <v>14.58449935913086</v>
       </c>
       <c r="C21" t="n">
         <v>27.94000053405762</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.14042186737061</v>
+        <v>15.14042472839355</v>
       </c>
       <c r="C22" t="n">
         <v>29.0049991607666</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.1702299118042</v>
+        <v>15.17023658752441</v>
       </c>
       <c r="C23" t="n">
         <v>28.86499977111816</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.8061637878418</v>
+        <v>15.80616188049316</v>
       </c>
       <c r="C24" t="n">
         <v>30.07500076293945</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>14.42571258544922</v>
+        <v>14.42571544647217</v>
       </c>
       <c r="C26" t="n">
         <v>27.26000022888184</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.81466484069824</v>
+        <v>14.81467247009277</v>
       </c>
       <c r="C27" t="n">
         <v>27.9950008392334</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.84394359588623</v>
+        <v>15.84394645690918</v>
       </c>
       <c r="C28" t="n">
         <v>29.94000053405762</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.08718109130859</v>
+        <v>16.08717918395996</v>
       </c>
       <c r="C29" t="n">
         <v>30.20000076293945</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.18572807312012</v>
+        <v>16.18572425842285</v>
       </c>
       <c r="C31" t="n">
         <v>30.38500022888184</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.27105522155762</v>
+        <v>17.27105712890625</v>
       </c>
       <c r="C32" t="n">
         <v>32.19499969482422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.75118637084961</v>
+        <v>17.75118827819824</v>
       </c>
       <c r="C33" t="n">
         <v>33.09000015258789</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.43248176574707</v>
+        <v>18.43247604370117</v>
       </c>
       <c r="C34" t="n">
         <v>34.36000061035156</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.28698348999023</v>
+        <v>18.2869758605957</v>
       </c>
       <c r="C35" t="n">
         <v>33.86999893188477</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.05327224731445</v>
+        <v>17.05327606201172</v>
       </c>
       <c r="C36" t="n">
         <v>31.58499908447266</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.39997291564941</v>
+        <v>16.39998054504395</v>
       </c>
       <c r="C37" t="n">
         <v>30.375</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>16.08559417724609</v>
+        <v>16.08559799194336</v>
       </c>
       <c r="C38" t="n">
         <v>29.57500076293945</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.27171611785889</v>
+        <v>14.27170562744141</v>
       </c>
       <c r="C39" t="n">
         <v>26.23999977111816</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.56465244293213</v>
+        <v>13.56465816497803</v>
       </c>
       <c r="C40" t="n">
         <v>24.94000053405762</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.902587890625</v>
+        <v>13.90259265899658</v>
       </c>
       <c r="C41" t="n">
         <v>25.34499931335449</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.0369815826416</v>
+        <v>14.03697776794434</v>
       </c>
       <c r="C42" t="n">
         <v>25.59000015258789</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.364426612854</v>
+        <v>15.36442947387695</v>
       </c>
       <c r="C43" t="n">
         <v>28.01000022888184</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.28485488891602</v>
+        <v>16.28486061096191</v>
       </c>
       <c r="C44" t="n">
         <v>29.45499992370605</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>16.51154136657715</v>
+        <v>16.51154518127441</v>
       </c>
       <c r="C45" t="n">
         <v>29.86499977111816</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.79696655273438</v>
+        <v>17.79696273803711</v>
       </c>
       <c r="C46" t="n">
         <v>32.18999862670898</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>18.3556022644043</v>
+        <v>18.35560417175293</v>
       </c>
       <c r="C47" t="n">
         <v>32.95999908447266</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.93478775024414</v>
+        <v>18.93478584289551</v>
       </c>
       <c r="C48" t="n">
         <v>34</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.71723747253418</v>
+        <v>19.71724319458008</v>
       </c>
       <c r="C49" t="n">
         <v>35.40499877929688</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.99512100219727</v>
+        <v>19.99512481689453</v>
       </c>
       <c r="C50" t="n">
         <v>35.65499877929688</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.19140625</v>
+        <v>20.19140815734863</v>
       </c>
       <c r="C51" t="n">
         <v>36.00500106811523</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>19.84932136535645</v>
+        <v>19.84931373596191</v>
       </c>
       <c r="C52" t="n">
         <v>35.39500045776367</v>
@@ -1493,7 +1505,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>20.11323165893555</v>
+        <v>20.11322784423828</v>
       </c>
       <c r="C54" t="n">
         <v>35.6150016784668</v>
@@ -1543,7 +1555,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.46367454528809</v>
+        <v>19.46367835998535</v>
       </c>
       <c r="C56" t="n">
         <v>34.20000076293945</v>
@@ -1597,11 +1609,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>20.57913398742676</v>
+        <v>20.57913970947266</v>
       </c>
       <c r="C57" t="n">
         <v>36.15999984741211</v>
@@ -1626,11 +1638,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>20.79540061950684</v>
+        <v>20.7953987121582</v>
       </c>
       <c r="C58" t="n">
         <v>36.54000091552734</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>21.53792381286621</v>
+        <v>21.53792190551758</v>
       </c>
       <c r="C59" t="n">
         <v>37.56000137329102</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.25918579101562</v>
+        <v>20.25917625427246</v>
       </c>
       <c r="C60" t="n">
         <v>35.33000183105469</v>
@@ -1713,11 +1725,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.40827178955078</v>
+        <v>20.40828132629395</v>
       </c>
       <c r="C61" t="n">
         <v>35.59000015258789</v>
@@ -1742,11 +1754,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.09746170043945</v>
+        <v>20.09746551513672</v>
       </c>
       <c r="C62" t="n">
         <v>34.77999877929688</v>
@@ -1771,11 +1783,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.4611701965332</v>
+        <v>21.46117210388184</v>
       </c>
       <c r="C63" t="n">
         <v>37.13999938964844</v>
@@ -1800,11 +1812,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>21.1202507019043</v>
+        <v>21.12024879455566</v>
       </c>
       <c r="C64" t="n">
         <v>36.54999923706055</v>
@@ -1829,11 +1841,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.46575355529785</v>
+        <v>22.46576499938965</v>
       </c>
       <c r="C65" t="n">
         <v>38.58000183105469</v>
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>23.15871238708496</v>
+        <v>23.15871810913086</v>
       </c>
       <c r="C66" t="n">
         <v>39.77000045776367</v>
@@ -1887,11 +1899,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.67380332946777</v>
+        <v>21.67380523681641</v>
       </c>
       <c r="C67" t="n">
         <v>37.22000122070312</v>
@@ -1916,11 +1928,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.9288158416748</v>
+        <v>21.92881774902344</v>
       </c>
       <c r="C68" t="n">
         <v>37.34999847412109</v>
@@ -1945,11 +1957,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.25760841369629</v>
+        <v>22.25759506225586</v>
       </c>
       <c r="C69" t="n">
         <v>37.90999984741211</v>
@@ -1974,11 +1986,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.59812927246094</v>
+        <v>22.5981388092041</v>
       </c>
       <c r="C70" t="n">
         <v>38.4900016784668</v>
@@ -2003,11 +2015,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.80445098876953</v>
+        <v>22.80446434020996</v>
       </c>
       <c r="C71" t="n">
         <v>38.52999877929688</v>
@@ -2026,7 +2038,7 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2049,11 +2061,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>23.91716003417969</v>
+        <v>23.91715431213379</v>
       </c>
       <c r="C73" t="n">
         <v>40.40999984741211</v>
@@ -2078,7 +2090,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2107,11 +2119,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>22.84537124633789</v>
+        <v>22.84538078308105</v>
       </c>
       <c r="C75" t="n">
         <v>38.31000137329102</v>
@@ -2136,11 +2148,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.52518081665039</v>
+        <v>23.52518463134766</v>
       </c>
       <c r="C76" t="n">
         <v>39.45000076293945</v>
@@ -2165,11 +2177,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.37082862854004</v>
+        <v>23.3708324432373</v>
       </c>
       <c r="C77" t="n">
         <v>38.88999938964844</v>
@@ -2194,11 +2206,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.0042552947998</v>
+        <v>23.00425148010254</v>
       </c>
       <c r="C78" t="n">
         <v>38.27999877929688</v>
@@ -2223,11 +2235,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.16049575805664</v>
+        <v>23.16049957275391</v>
       </c>
       <c r="C79" t="n">
         <v>38.54000091552734</v>
@@ -2252,11 +2264,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>23.45491600036621</v>
+        <v>23.45491218566895</v>
       </c>
       <c r="C80" t="n">
         <v>38.70000076293945</v>
@@ -2281,11 +2293,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>23.83674049377441</v>
+        <v>23.83673858642578</v>
       </c>
       <c r="C81" t="n">
         <v>39.33000183105469</v>
@@ -2310,11 +2322,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.15188980102539</v>
+        <v>24.15188789367676</v>
       </c>
       <c r="C82" t="n">
         <v>39.84999847412109</v>
@@ -2339,11 +2351,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.49174118041992</v>
+        <v>24.49175071716309</v>
       </c>
       <c r="C83" t="n">
         <v>40.08000183105469</v>
@@ -2368,7 +2380,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2397,11 +2409,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.69950103759766</v>
+        <v>24.69950675964355</v>
       </c>
       <c r="C85" t="n">
         <v>40.41999816894531</v>
@@ -2426,11 +2438,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>25.83327293395996</v>
+        <v>25.83326530456543</v>
       </c>
       <c r="C86" t="n">
         <v>41.93999862670898</v>
@@ -2455,7 +2467,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2484,11 +2496,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>30.37287139892578</v>
+        <v>30.37286376953125</v>
       </c>
       <c r="C88" t="n">
         <v>49.31000137329102</v>
@@ -2513,11 +2525,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>31.26828193664551</v>
+        <v>31.2682991027832</v>
       </c>
       <c r="C89" t="n">
         <v>50.41999816894531</v>
@@ -2542,11 +2554,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.19696998596191</v>
+        <v>29.19696807861328</v>
       </c>
       <c r="C90" t="n">
         <v>47.08000183105469</v>
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>30.09619903564453</v>
+        <v>30.09618759155273</v>
       </c>
       <c r="C91" t="n">
         <v>48.52999877929688</v>
@@ -2600,7 +2612,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2629,11 +2641,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>30.82501029968262</v>
+        <v>30.82502555847168</v>
       </c>
       <c r="C93" t="n">
         <v>49.31999969482422</v>
@@ -2658,11 +2670,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>29.95001029968262</v>
+        <v>29.95001792907715</v>
       </c>
       <c r="C94" t="n">
         <v>47.91999816894531</v>
@@ -2687,11 +2699,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.7640380859375</v>
+        <v>31.76404190063477</v>
       </c>
       <c r="C95" t="n">
         <v>50.41999816894531</v>
@@ -2716,11 +2728,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.77033042907715</v>
+        <v>31.77034568786621</v>
       </c>
       <c r="C96" t="n">
         <v>50.43000030517578</v>
@@ -2745,11 +2757,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.44274139404297</v>
+        <v>31.44275283813477</v>
       </c>
       <c r="C97" t="n">
         <v>49.90999984741211</v>
@@ -2774,11 +2786,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.48444557189941</v>
+        <v>30.48445129394531</v>
       </c>
       <c r="C98" t="n">
         <v>48.02000045776367</v>
@@ -2803,11 +2815,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.76045417785645</v>
+        <v>31.76044464111328</v>
       </c>
       <c r="C99" t="n">
         <v>50.02999877929688</v>
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2861,11 +2873,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.92685317993164</v>
+        <v>33.92686080932617</v>
       </c>
       <c r="C101" t="n">
         <v>53.02000045776367</v>
@@ -2890,7 +2902,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2919,11 +2931,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.61971282958984</v>
+        <v>33.61972427368164</v>
       </c>
       <c r="C103" t="n">
         <v>52.54000091552734</v>
@@ -2948,11 +2960,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.33859252929688</v>
+        <v>32.33860397338867</v>
       </c>
       <c r="C104" t="n">
         <v>50.15000152587891</v>
@@ -2977,11 +2989,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>34.42141723632812</v>
+        <v>34.42140579223633</v>
       </c>
       <c r="C105" t="n">
         <v>53.38000106811523</v>
@@ -3006,11 +3018,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.53203582763672</v>
+        <v>32.53203964233398</v>
       </c>
       <c r="C106" t="n">
         <v>50.45000076293945</v>
@@ -3035,11 +3047,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>33.78175735473633</v>
+        <v>33.78176116943359</v>
       </c>
       <c r="C107" t="n">
         <v>51.95999908447266</v>
@@ -3064,11 +3076,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>34.29537582397461</v>
+        <v>34.29538345336914</v>
       </c>
       <c r="C108" t="n">
         <v>52.75</v>
@@ -3093,11 +3105,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>34.6724739074707</v>
+        <v>34.67246627807617</v>
       </c>
       <c r="C109" t="n">
         <v>53.33000183105469</v>
@@ -3122,7 +3134,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3151,11 +3163,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>35.24354553222656</v>
+        <v>35.24354934692383</v>
       </c>
       <c r="C111" t="n">
         <v>53.79000091552734</v>
@@ -3180,11 +3192,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.08467864990234</v>
+        <v>37.08468627929688</v>
       </c>
       <c r="C112" t="n">
         <v>56.59999847412109</v>
@@ -3209,11 +3221,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>36.54586029052734</v>
+        <v>36.54584884643555</v>
       </c>
       <c r="C113" t="n">
         <v>55.34000015258789</v>
@@ -3238,11 +3250,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>37.08078002929688</v>
+        <v>37.08076477050781</v>
       </c>
       <c r="C114" t="n">
         <v>56.15000152587891</v>
@@ -3267,7 +3279,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3296,11 +3308,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>38.73559188842773</v>
+        <v>38.73558807373047</v>
       </c>
       <c r="C116" t="n">
         <v>58.20999908447266</v>
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3354,7 +3366,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3383,11 +3395,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.97693634033203</v>
+        <v>38.97693252563477</v>
       </c>
       <c r="C119" t="n">
         <v>58.11000061035156</v>
@@ -3412,7 +3424,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3441,11 +3453,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>38.67510986328125</v>
+        <v>38.67510604858398</v>
       </c>
       <c r="C121" t="n">
         <v>57.65999984741211</v>
@@ -3470,11 +3482,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>38.20003509521484</v>
+        <v>38.20002365112305</v>
       </c>
       <c r="C122" t="n">
         <v>56.5099983215332</v>
@@ -3499,7 +3511,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3528,7 +3540,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3557,11 +3569,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>41.76457595825195</v>
+        <v>41.76456832885742</v>
       </c>
       <c r="C125" t="n">
         <v>61.34000015258789</v>
@@ -3586,11 +3598,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>42.74502563476562</v>
+        <v>42.74502944946289</v>
       </c>
       <c r="C126" t="n">
         <v>62.77999877929688</v>
@@ -3615,11 +3627,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.55965042114258</v>
+        <v>48.55964279174805</v>
       </c>
       <c r="C127" t="n">
         <v>71.31999969482422</v>
@@ -3644,11 +3656,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>49.27369689941406</v>
+        <v>49.27370452880859</v>
       </c>
       <c r="C128" t="n">
         <v>71.88999938964844</v>
@@ -3673,11 +3685,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>48.54032516479492</v>
+        <v>48.54033660888672</v>
       </c>
       <c r="C129" t="n">
         <v>70.81999969482422</v>
@@ -3702,11 +3714,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>43.78361892700195</v>
+        <v>43.78361511230469</v>
       </c>
       <c r="C130" t="n">
         <v>63.88000106811523</v>
@@ -3731,11 +3743,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>42.80725479125977</v>
+        <v>42.80724334716797</v>
       </c>
       <c r="C131" t="n">
         <v>61.97999954223633</v>
@@ -3760,11 +3772,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>42.08896255493164</v>
+        <v>42.08897018432617</v>
       </c>
       <c r="C132" t="n">
         <v>60.93999862670898</v>
@@ -3789,11 +3801,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>42.66220855712891</v>
+        <v>42.66220474243164</v>
       </c>
       <c r="C133" t="n">
         <v>61.77000045776367</v>
@@ -3818,11 +3830,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>43.4879035949707</v>
+        <v>43.48789978027344</v>
       </c>
       <c r="C134" t="n">
         <v>62.47999954223633</v>
@@ -3847,11 +3859,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>42.01927947998047</v>
+        <v>42.019287109375</v>
       </c>
       <c r="C135" t="n">
         <v>60.36999893188477</v>
@@ -3876,11 +3888,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>41.07268524169922</v>
+        <v>41.07267379760742</v>
       </c>
       <c r="C136" t="n">
         <v>59.0099983215332</v>
@@ -3905,11 +3917,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>40.36123275756836</v>
+        <v>40.36122512817383</v>
       </c>
       <c r="C137" t="n">
         <v>57.5099983215332</v>
@@ -3934,11 +3946,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>39.82083511352539</v>
+        <v>39.82083129882812</v>
       </c>
       <c r="C138" t="n">
         <v>56.7400016784668</v>
@@ -3963,11 +3975,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>38.88039779663086</v>
+        <v>38.88040542602539</v>
       </c>
       <c r="C139" t="n">
         <v>55.40000152587891</v>
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>37.71570205688477</v>
+        <v>37.71570587158203</v>
       </c>
       <c r="C141" t="n">
         <v>53.2599983215332</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>36.65349578857422</v>
+        <v>36.65348815917969</v>
       </c>
       <c r="C142" t="n">
         <v>51.7599983215332</v>
@@ -4079,11 +4091,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>37.11593627929688</v>
+        <v>37.11594009399414</v>
       </c>
       <c r="C143" t="n">
         <v>51.91999816894531</v>
@@ -4108,11 +4120,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.43291854858398</v>
+        <v>40.43291473388672</v>
       </c>
       <c r="C144" t="n">
         <v>56.56000137329102</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>42.38452529907227</v>
+        <v>42.38450241088867</v>
       </c>
       <c r="C145" t="n">
         <v>59.29000091552734</v>
@@ -4166,11 +4178,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>42.15620803833008</v>
+        <v>42.15620422363281</v>
       </c>
       <c r="C146" t="n">
         <v>58.4900016784668</v>
@@ -4195,11 +4207,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.43350982666016</v>
+        <v>36.43352127075195</v>
       </c>
       <c r="C147" t="n">
         <v>50.54999923706055</v>
@@ -4224,11 +4236,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.47664260864258</v>
+        <v>32.47663116455078</v>
       </c>
       <c r="C148" t="n">
         <v>45.06000137329102</v>
@@ -4253,11 +4265,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>31.86867713928223</v>
+        <v>31.86867904663086</v>
       </c>
       <c r="C149" t="n">
         <v>43.7400016784668</v>
@@ -4282,11 +4294,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>30.81222534179688</v>
+        <v>30.81222915649414</v>
       </c>
       <c r="C150" t="n">
         <v>42.29000091552734</v>
@@ -4311,7 +4323,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4340,11 +4352,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>33.92814636230469</v>
+        <v>33.92813873291016</v>
       </c>
       <c r="C152" t="n">
         <v>46.06000137329102</v>
@@ -4369,7 +4381,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4398,11 +4410,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>31.61519432067871</v>
+        <v>31.61519241333008</v>
       </c>
       <c r="C154" t="n">
         <v>42.91999816894531</v>
@@ -4427,11 +4439,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>32.62351226806641</v>
+        <v>32.6235237121582</v>
       </c>
       <c r="C155" t="n">
         <v>43.79999923706055</v>
@@ -4456,11 +4468,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>31.51372146606445</v>
+        <v>31.51371955871582</v>
       </c>
       <c r="C156" t="n">
         <v>42.31000137329102</v>
@@ -4485,11 +4497,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.00364112854004</v>
+        <v>29.00364685058594</v>
       </c>
       <c r="C157" t="n">
         <v>38.93999862670898</v>
@@ -4514,11 +4526,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>33.49969863891602</v>
+        <v>33.49970245361328</v>
       </c>
       <c r="C158" t="n">
         <v>44.43999862670898</v>
@@ -4543,11 +4555,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.5274658203125</v>
+        <v>35.52746200561523</v>
       </c>
       <c r="C159" t="n">
         <v>47.13000106811523</v>
@@ -4572,11 +4584,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>39.01010894775391</v>
+        <v>39.01010131835938</v>
       </c>
       <c r="C160" t="n">
         <v>51.75</v>
@@ -4601,11 +4613,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.17313003540039</v>
+        <v>39.17314147949219</v>
       </c>
       <c r="C161" t="n">
         <v>51.47000122070312</v>
@@ -4630,11 +4642,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>37.62812042236328</v>
+        <v>37.62813186645508</v>
       </c>
       <c r="C162" t="n">
         <v>49.43999862670898</v>
@@ -4659,11 +4671,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.97228240966797</v>
+        <v>39.97227478027344</v>
       </c>
       <c r="C163" t="n">
         <v>52.52000045776367</v>
@@ -4688,11 +4700,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>40.79111480712891</v>
+        <v>40.79111099243164</v>
       </c>
       <c r="C164" t="n">
         <v>53.11000061035156</v>
@@ -4717,11 +4729,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>41.32107543945312</v>
+        <v>41.32107162475586</v>
       </c>
       <c r="C165" t="n">
         <v>53.79999923706055</v>
@@ -4746,11 +4758,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>42.33489990234375</v>
+        <v>42.33489608764648</v>
       </c>
       <c r="C166" t="n">
         <v>55.11999893188477</v>
@@ -4775,11 +4787,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>39.41971206665039</v>
+        <v>39.41970443725586</v>
       </c>
       <c r="C167" t="n">
         <v>50.86000061035156</v>
@@ -4804,11 +4816,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>41.32637023925781</v>
+        <v>41.32636642456055</v>
       </c>
       <c r="C168" t="n">
         <v>53.31999969482422</v>
@@ -4833,7 +4845,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4862,11 +4874,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>40.85162353515625</v>
+        <v>40.85162734985352</v>
       </c>
       <c r="C170" t="n">
         <v>52.22000122070312</v>
@@ -4891,11 +4903,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.33262252807617</v>
+        <v>38.33261489868164</v>
       </c>
       <c r="C171" t="n">
         <v>49</v>
@@ -4920,11 +4932,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>41.28190231323242</v>
+        <v>41.28189468383789</v>
       </c>
       <c r="C172" t="n">
         <v>52.77000045776367</v>
@@ -4949,11 +4961,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>47.26217651367188</v>
+        <v>47.26216888427734</v>
       </c>
       <c r="C173" t="n">
         <v>59.88999938964844</v>
@@ -4978,11 +4990,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>49.74800109863281</v>
+        <v>49.74799346923828</v>
       </c>
       <c r="C174" t="n">
         <v>63.04000091552734</v>
@@ -5007,11 +5019,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>48.65108108520508</v>
+        <v>48.65107345581055</v>
       </c>
       <c r="C175" t="n">
         <v>61.65000152587891</v>
@@ -5036,11 +5048,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>50.32126235961914</v>
+        <v>50.32126998901367</v>
       </c>
       <c r="C176" t="n">
         <v>63.27000045776367</v>
@@ -5065,11 +5077,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>50.86208343505859</v>
+        <v>50.86209869384766</v>
       </c>
       <c r="C177" t="n">
         <v>63.95000076293945</v>
@@ -5094,11 +5106,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>49.05666732788086</v>
+        <v>49.05667114257812</v>
       </c>
       <c r="C178" t="n">
         <v>61.68000030517578</v>
@@ -5123,11 +5135,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>47.41320419311523</v>
+        <v>47.41320037841797</v>
       </c>
       <c r="C179" t="n">
         <v>59.11999893188477</v>
@@ -5152,11 +5164,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>48.77658081054688</v>
+        <v>48.77657699584961</v>
       </c>
       <c r="C180" t="n">
         <v>60.81999969482422</v>
@@ -5181,7 +5193,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5210,11 +5222,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>47.00188064575195</v>
+        <v>47.00188446044922</v>
       </c>
       <c r="C182" t="n">
         <v>58.09999847412109</v>
@@ -5239,11 +5251,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>44.50212478637695</v>
+        <v>44.50212097167969</v>
       </c>
       <c r="C183" t="n">
         <v>55.0099983215332</v>
@@ -5268,11 +5280,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>49.60679626464844</v>
+        <v>49.60680770874023</v>
       </c>
       <c r="C184" t="n">
         <v>61.31999969482422</v>
@@ -5297,7 +5309,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5326,7 +5338,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5355,11 +5367,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>49.70421981811523</v>
+        <v>49.7042236328125</v>
       </c>
       <c r="C187" t="n">
         <v>60.93000030517578</v>
@@ -5384,11 +5396,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.42455291748047</v>
+        <v>48.42454528808594</v>
       </c>
       <c r="C188" t="n">
         <v>58.86000061035156</v>
@@ -5413,11 +5425,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>47.56069564819336</v>
+        <v>47.56070709228516</v>
       </c>
       <c r="C189" t="n">
         <v>57.81000137329102</v>
@@ -5442,11 +5454,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.21433639526367</v>
+        <v>49.2143440246582</v>
       </c>
       <c r="C190" t="n">
         <v>59.81999969482422</v>
@@ -5471,11 +5483,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>51.26410675048828</v>
+        <v>51.26411056518555</v>
       </c>
       <c r="C191" t="n">
         <v>61.79999923706055</v>
@@ -5500,11 +5512,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>51.23923492431641</v>
+        <v>51.23921966552734</v>
       </c>
       <c r="C192" t="n">
         <v>61.77000045776367</v>
@@ -5529,11 +5541,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>55.89280319213867</v>
+        <v>55.89280700683594</v>
       </c>
       <c r="C193" t="n">
         <v>67.37999725341797</v>
@@ -5558,11 +5570,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>57.39859390258789</v>
+        <v>57.39859771728516</v>
       </c>
       <c r="C194" t="n">
         <v>68.68000030517578</v>
@@ -5587,11 +5599,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>56.35391998291016</v>
+        <v>56.35391616821289</v>
       </c>
       <c r="C195" t="n">
         <v>67.43000030517578</v>
@@ -5616,11 +5628,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>56.59628295898438</v>
+        <v>56.59628677368164</v>
       </c>
       <c r="C196" t="n">
         <v>67.72000122070312</v>
@@ -5645,11 +5657,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>59.54737854003906</v>
+        <v>59.54740142822266</v>
       </c>
       <c r="C197" t="n">
         <v>70.73000335693359</v>
@@ -5674,11 +5686,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>58.80651473999023</v>
+        <v>58.80651092529297</v>
       </c>
       <c r="C198" t="n">
         <v>69.84999847412109</v>
@@ -5703,11 +5715,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>63.52114868164062</v>
+        <v>63.52113342285156</v>
       </c>
       <c r="C199" t="n">
         <v>75.44999694824219</v>
@@ -5732,11 +5744,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>63.41474533081055</v>
+        <v>63.41476821899414</v>
       </c>
       <c r="C200" t="n">
         <v>74.79000091552734</v>
@@ -5761,7 +5773,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5790,7 +5802,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5819,11 +5831,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>69.65618896484375</v>
+        <v>69.65619659423828</v>
       </c>
       <c r="C203" t="n">
         <v>81.58000183105469</v>
@@ -5848,11 +5860,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>72.83248901367188</v>
+        <v>72.83248138427734</v>
       </c>
       <c r="C204" t="n">
         <v>85.30000305175781</v>
@@ -5877,11 +5889,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>71.59439849853516</v>
+        <v>71.59441375732422</v>
       </c>
       <c r="C205" t="n">
         <v>83.84999847412109</v>
@@ -5906,11 +5918,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>67.32978057861328</v>
+        <v>67.32978820800781</v>
       </c>
       <c r="C206" t="n">
         <v>78.36000061035156</v>
@@ -5935,7 +5947,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5964,7 +5976,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5993,11 +6005,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>76.62945556640625</v>
+        <v>76.62946319580078</v>
       </c>
       <c r="C209" t="n">
         <v>88.62999725341797</v>
@@ -6022,11 +6034,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>72.76470184326172</v>
+        <v>72.76470947265625</v>
       </c>
       <c r="C210" t="n">
         <v>84.16000366210938</v>
@@ -6051,7 +6063,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6080,11 +6092,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>65.12288665771484</v>
+        <v>65.12287902832031</v>
       </c>
       <c r="C212" t="n">
         <v>74.73999786376953</v>
@@ -6109,11 +6121,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>58.95389938354492</v>
+        <v>58.95390319824219</v>
       </c>
       <c r="C213" t="n">
         <v>67.66000366210938</v>
@@ -6138,11 +6150,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>55.75613021850586</v>
+        <v>55.75613403320312</v>
       </c>
       <c r="C214" t="n">
         <v>63.9900016784668</v>
@@ -6167,11 +6179,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>57.38824844360352</v>
+        <v>57.38825225830078</v>
       </c>
       <c r="C215" t="n">
         <v>65.23999786376953</v>
@@ -6196,11 +6208,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.99840545654297</v>
+        <v>55.9984016418457</v>
       </c>
       <c r="C216" t="n">
         <v>63.65999984741211</v>
@@ -6225,11 +6237,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>57.30028533935547</v>
+        <v>57.30027389526367</v>
       </c>
       <c r="C217" t="n">
         <v>65.13999938964844</v>
@@ -6254,7 +6266,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6283,11 +6295,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>56.97586822509766</v>
+        <v>56.97586441040039</v>
       </c>
       <c r="C219" t="n">
         <v>64.18000030517578</v>
@@ -6312,7 +6324,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6341,11 +6353,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>63.08264923095703</v>
+        <v>63.08263778686523</v>
       </c>
       <c r="C221" t="n">
         <v>70.45999908447266</v>
@@ -6370,11 +6382,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>61.55168151855469</v>
+        <v>61.55168533325195</v>
       </c>
       <c r="C222" t="n">
         <v>68.75</v>
@@ -6399,11 +6411,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>56.63650131225586</v>
+        <v>56.63650512695312</v>
       </c>
       <c r="C223" t="n">
         <v>63.2599983215332</v>
@@ -6428,7 +6440,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6457,7 +6469,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6486,11 +6498,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>66.75662231445312</v>
+        <v>66.75661468505859</v>
       </c>
       <c r="C226" t="n">
         <v>73.84999847412109</v>
@@ -6515,7 +6527,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6544,11 +6556,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>60.39847946166992</v>
+        <v>60.39848709106445</v>
       </c>
       <c r="C228" t="n">
         <v>66.26000213623047</v>
@@ -6573,11 +6585,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>58.12874984741211</v>
+        <v>58.12875366210938</v>
       </c>
       <c r="C229" t="n">
         <v>63.77000045776367</v>
@@ -6602,11 +6614,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>55.36471176147461</v>
+        <v>55.36470794677734</v>
       </c>
       <c r="C230" t="n">
         <v>60.13999938964844</v>
@@ -6631,7 +6643,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6660,11 +6672,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>55.04250335693359</v>
+        <v>55.04249954223633</v>
       </c>
       <c r="C232" t="n">
         <v>59.79000091552734</v>
@@ -6689,11 +6701,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>52.78011322021484</v>
+        <v>52.78011703491211</v>
       </c>
       <c r="C233" t="n">
         <v>56.7400016784668</v>
@@ -6718,11 +6730,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>50.47319030761719</v>
+        <v>50.47319412231445</v>
       </c>
       <c r="C234" t="n">
         <v>54.2599983215332</v>
@@ -6747,7 +6759,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6776,11 +6788,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>46.11105346679688</v>
+        <v>46.11105728149414</v>
       </c>
       <c r="C236" t="n">
         <v>48.97999954223633</v>
@@ -6805,7 +6817,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6834,7 +6846,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6863,7 +6875,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6892,11 +6904,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>45.13603210449219</v>
+        <v>45.13602828979492</v>
       </c>
       <c r="C240" t="n">
         <v>47.34999847412109</v>
@@ -6921,7 +6933,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6950,7 +6962,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6979,11 +6991,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>43.722412109375</v>
+        <v>43.72241592407227</v>
       </c>
       <c r="C243" t="n">
         <v>45.22999954223633</v>
@@ -7008,7 +7020,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7037,7 +7049,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7066,7 +7078,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7095,7 +7107,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7124,7 +7136,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7151,7 +7163,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,17 +7190,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>35.81999969482422</v>
+        <v>34.83000183105469</v>
       </c>
       <c r="C250" t="n">
-        <v>35.81999969482422</v>
+        <v>34.83000183105469</v>
       </c>
       <c r="D250" t="n">
-        <v>158262600</v>
+        <v>170805000</v>
       </c>
       <c r="E250" t="n">
         <v>-1.66</v>
@@ -7198,10 +7210,10 @@
         <v>534687144</v>
       </c>
       <c r="H250" t="n">
-        <v>19152493334.90643</v>
+        <v>18623154204.5614</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2959910328421885</v>
+        <v>0.3194484885538972</v>
       </c>
     </row>
   </sheetData>
@@ -7233,75 +7245,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39594</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39684</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40080</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7337,13 +7349,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39685</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39775</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7379,13 +7391,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39776</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39866</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40261</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7421,13 +7433,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39867</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7454,7 +7466,7 @@
       <c r="I5" t="n">
         <v>1.9</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="K5" t="n">
@@ -7467,13 +7479,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40055</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40080</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7500,7 +7512,7 @@
       <c r="I6" t="n">
         <v>2.13</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="K6" t="n">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40146</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7546,7 +7558,7 @@
       <c r="I7" t="n">
         <v>2.415</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="K7" t="n">
@@ -7559,13 +7571,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40261</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7592,7 +7604,7 @@
       <c r="I8" t="n">
         <v>2.47</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="K8" t="n">
@@ -7605,13 +7617,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40328</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7638,7 +7650,7 @@
       <c r="I9" t="n">
         <v>2.24</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="K9" t="n">
@@ -7651,13 +7663,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40419</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40443</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7684,7 +7696,7 @@
       <c r="I10" t="n">
         <v>2.315</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40443</v>
       </c>
       <c r="K10" t="n">
@@ -7697,13 +7709,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40420</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40510</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7730,7 +7742,7 @@
       <c r="I11" t="n">
         <v>2.405</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K11" t="n">
@@ -7743,13 +7755,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40511</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40601</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7776,7 +7788,7 @@
       <c r="I12" t="n">
         <v>2.515</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="K12" t="n">
@@ -7789,13 +7801,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40692</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40732</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7822,7 +7834,7 @@
       <c r="I13" t="n">
         <v>2.69</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40732</v>
       </c>
       <c r="K13" t="n">
@@ -7835,13 +7847,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40693</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40783</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40807</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7868,7 +7880,7 @@
       <c r="I14" t="n">
         <v>2.6</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40807</v>
       </c>
       <c r="K14" t="n">
@@ -7881,13 +7893,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40784</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40874</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7914,7 +7926,7 @@
       <c r="I15" t="n">
         <v>2.35</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="K15" t="n">
@@ -7927,13 +7939,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40875</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40965</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40989</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7960,7 +7972,7 @@
       <c r="I16" t="n">
         <v>2.34</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40989</v>
       </c>
       <c r="K16" t="n">
@@ -7973,13 +7985,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40966</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41056</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41093</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8006,7 +8018,7 @@
       <c r="I17" t="n">
         <v>2.35</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41093</v>
       </c>
       <c r="K17" t="n">
@@ -8019,13 +8031,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41057</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41147</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8052,7 +8064,7 @@
       <c r="I18" t="n">
         <v>2.56</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="K18" t="n">
@@ -8065,13 +8077,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41148</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41238</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41262</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8098,7 +8110,7 @@
       <c r="I19" t="n">
         <v>2.71</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41262</v>
       </c>
       <c r="K19" t="n">
@@ -8111,13 +8123,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41239</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41329</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8144,7 +8156,7 @@
       <c r="I20" t="n">
         <v>2.73</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="K20" t="n">
@@ -8157,13 +8169,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41330</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41420</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41458</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8190,7 +8202,7 @@
       <c r="I21" t="n">
         <v>2.79</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41458</v>
       </c>
       <c r="K21" t="n">
@@ -8203,13 +8215,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41421</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41511</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41535</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8236,7 +8248,7 @@
       <c r="I22" t="n">
         <v>2.67</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41535</v>
       </c>
       <c r="K22" t="n">
@@ -8249,13 +8261,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41512</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41602</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41626</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8282,7 +8294,7 @@
       <c r="I23" t="n">
         <v>2.69</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41626</v>
       </c>
       <c r="K23" t="n">
@@ -8295,13 +8307,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41603</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41693</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41717</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8328,7 +8340,7 @@
       <c r="I24" t="n">
         <v>2.73</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41717</v>
       </c>
       <c r="K24" t="n">
@@ -8341,13 +8353,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41694</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41784</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8374,7 +8386,7 @@
       <c r="I25" t="n">
         <v>2.83</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="K25" t="n">
@@ -8387,13 +8399,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41785</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41875</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8420,7 +8432,7 @@
       <c r="I26" t="n">
         <v>2.68</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="K26" t="n">
@@ -8433,13 +8445,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41876</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41966</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8466,7 +8478,7 @@
       <c r="I27" t="n">
         <v>2.4</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="K27" t="n">
@@ -8479,13 +8491,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41967</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42057</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42081</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8512,7 +8524,7 @@
       <c r="I28" t="n">
         <v>2.32</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42081</v>
       </c>
       <c r="K28" t="n">
@@ -8525,13 +8537,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42058</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42191</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8558,7 +8570,7 @@
       <c r="I29" t="n">
         <v>1.97</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42191</v>
       </c>
       <c r="K29" t="n">
@@ -8571,13 +8583,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42246</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8604,7 +8616,7 @@
       <c r="I30" t="n">
         <v>2.11</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="K30" t="n">
@@ -8617,13 +8629,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42337</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8650,7 +8662,7 @@
       <c r="I31" t="n">
         <v>2.42</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="K31" t="n">
@@ -8663,13 +8675,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42428</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42452</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8696,7 +8708,7 @@
       <c r="I32" t="n">
         <v>2.45</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42452</v>
       </c>
       <c r="K32" t="n">
@@ -8709,13 +8721,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42519</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8742,7 +8754,7 @@
       <c r="I33" t="n">
         <v>2.77</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="K33" t="n">
@@ -8755,13 +8767,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42520</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42610</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8788,7 +8800,7 @@
       <c r="I34" t="n">
         <v>2.75</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="K34" t="n">
@@ -8801,13 +8813,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42611</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42701</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42724</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8834,7 +8846,7 @@
       <c r="I35" t="n">
         <v>2.68</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42724</v>
       </c>
       <c r="K35" t="n">
@@ -8847,13 +8859,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42702</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42792</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42815</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8880,7 +8892,7 @@
       <c r="I36" t="n">
         <v>2.7</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42815</v>
       </c>
       <c r="K36" t="n">
@@ -8893,13 +8905,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42793</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42883</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42915</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8926,7 +8938,7 @@
       <c r="I37" t="n">
         <v>2.77</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42915</v>
       </c>
       <c r="K37" t="n">
@@ -8939,13 +8951,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42884</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42974</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8972,7 +8984,7 @@
       <c r="I38" t="n">
         <v>2.79</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="K38" t="n">
@@ -8985,13 +8997,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42975</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43065</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="I39" t="n">
         <v>2.73</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="K39" t="n">
@@ -9031,13 +9043,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43066</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43156</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9064,7 +9076,7 @@
       <c r="I40" t="n">
         <v>3.74</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="K40" t="n">
@@ -9077,13 +9089,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43157</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43247</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9110,7 +9122,7 @@
       <c r="I41" t="n">
         <v>3.64</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="K41" t="n">
@@ -9123,13 +9135,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43248</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43338</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43361</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9156,7 +9168,7 @@
       <c r="I42" t="n">
         <v>3.600000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43361</v>
       </c>
       <c r="K42" t="n">
@@ -9169,13 +9181,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43339</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43429</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9202,7 +9214,7 @@
       <c r="I43" t="n">
         <v>3.43</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="K43" t="n">
@@ -9215,13 +9227,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43430</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43520</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43544</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9248,7 +9260,7 @@
       <c r="I44" t="n">
         <v>2.55</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43544</v>
       </c>
       <c r="K44" t="n">
@@ -9261,13 +9273,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43521</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43611</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9294,7 +9306,7 @@
       <c r="I45" t="n">
         <v>2.9</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="K45" t="n">
@@ -9307,13 +9319,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43612</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43702</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43726</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9340,7 +9352,7 @@
       <c r="I46" t="n">
         <v>3.1</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43726</v>
       </c>
       <c r="K46" t="n">
@@ -9353,13 +9365,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43703</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43793</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43817</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9386,7 +9398,7 @@
       <c r="I47" t="n">
         <v>3.48</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43817</v>
       </c>
       <c r="K47" t="n">
@@ -9399,13 +9411,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43794</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43884</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9432,7 +9444,7 @@
       <c r="I48" t="n">
         <v>3.48</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="K48" t="n">
@@ -9445,13 +9457,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43885</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44014</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9478,7 +9490,7 @@
       <c r="I49" t="n">
         <v>3.56</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44014</v>
       </c>
       <c r="K49" t="n">
@@ -9491,13 +9503,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44073</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9524,7 +9536,7 @@
       <c r="I50" t="n">
         <v>3.74</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="K50" t="n">
@@ -9537,13 +9549,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44164</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9570,7 +9582,7 @@
       <c r="I51" t="n">
         <v>3.9</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="K51" t="n">
@@ -9583,13 +9595,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9616,7 +9628,7 @@
       <c r="I52" t="n">
         <v>4.12</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="K52" t="n">
@@ -9629,13 +9641,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44346</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9662,7 +9674,7 @@
       <c r="I53" t="n">
         <v>3.78</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="K53" t="n">
@@ -9675,13 +9687,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44437</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44461</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9708,7 +9720,7 @@
       <c r="I54" t="n">
         <v>3.77</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44461</v>
       </c>
       <c r="K54" t="n">
@@ -9721,13 +9733,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44438</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44528</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44551</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9754,7 +9766,7 @@
       <c r="I55" t="n">
         <v>3.63</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44551</v>
       </c>
       <c r="K55" t="n">
@@ -9767,13 +9779,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44529</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44619</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9800,7 +9812,7 @@
       <c r="I56" t="n">
         <v>3.75</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="K56" t="n">
@@ -9813,13 +9825,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44710</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9846,7 +9858,7 @@
       <c r="I57" t="n">
         <v>4.42</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="K57" t="n">
@@ -9859,13 +9871,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44711</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44801</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44825</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9892,7 +9904,7 @@
       <c r="I58" t="n">
         <v>4.75</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44825</v>
       </c>
       <c r="K58" t="n">
@@ -9905,13 +9917,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44802</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44892</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9938,7 +9950,7 @@
       <c r="I59" t="n">
         <v>4.790000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="K59" t="n">
@@ -9951,13 +9963,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44893</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44983</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9984,7 +9996,7 @@
       <c r="I60" t="n">
         <v>4.630000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="K60" t="n">
@@ -9997,13 +10009,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45074</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10030,7 +10042,7 @@
       <c r="I61" t="n">
         <v>4.31</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="K61" t="n">
@@ -10043,13 +10055,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45075</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45165</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10076,7 +10088,7 @@
       <c r="I62" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="K62" t="n">
@@ -10089,13 +10101,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45166</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45256</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10122,7 +10134,7 @@
       <c r="I63" t="n">
         <v>4.11</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="K63" t="n">
@@ -10135,13 +10147,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45257</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45347</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10168,7 +10180,7 @@
       <c r="I64" t="n">
         <v>4.36</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="K64" t="n">
@@ -10181,13 +10193,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45349</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45438</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10214,7 +10226,7 @@
       <c r="I65" t="n">
         <v>4.31</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="K65" t="n">
@@ -10227,13 +10239,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45439</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45529</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10260,7 +10272,7 @@
       <c r="I66" t="n">
         <v>4.2</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="K66" t="n">
@@ -10273,13 +10285,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45530</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45620</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10306,7 +10318,7 @@
       <c r="I67" t="n">
         <v>4.6</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="K67" t="n">
@@ -10319,13 +10331,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45621</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45711</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45735</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10352,7 +10364,7 @@
       <c r="I68" t="n">
         <v>4.55</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45735</v>
       </c>
       <c r="K68" t="n">
@@ -10365,13 +10377,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45712</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45802</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10398,7 +10410,7 @@
       <c r="I69" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="K69" t="n">
@@ -10411,13 +10423,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45803</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45893</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45917</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10444,7 +10456,7 @@
       <c r="I70" t="n">
         <v>5.29</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45917</v>
       </c>
       <c r="K70" t="n">
@@ -10457,13 +10469,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45894</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10490,7 +10502,7 @@
       <c r="I71" t="n">
         <v>4.65</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="K71" t="n">
@@ -10503,13 +10515,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45985</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10536,7 +10548,7 @@
       <c r="I72" t="n">
         <v>4.09</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="K72" t="n">
@@ -10549,13 +10561,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10582,7 +10594,7 @@
       <c r="I73" t="n">
         <v>-0.1800000000000006</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="K73" t="n">
@@ -10595,13 +10607,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46174</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46264</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10628,7 +10640,7 @@
       <c r="I74" t="n">
         <v>-1.66</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="K74" t="n">
@@ -10665,52 +10677,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40055</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40080</v>
       </c>
       <c r="C2" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40146</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="C3" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40261</v>
       </c>
       <c r="C4" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40347</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40368</v>
       </c>
       <c r="C5" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40434</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40443</v>
       </c>
       <c r="C6" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40522</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="C7" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40601</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40625</v>
       </c>
       <c r="C8" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40874</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="C9" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40965</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40989</v>
       </c>
       <c r="C10" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41075</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41093</v>
       </c>
       <c r="C11" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41151</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41171</v>
       </c>
       <c r="C12" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41250</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41262</v>
       </c>
       <c r="C13" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41341</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="C14" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41439</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41458</v>
       </c>
       <c r="C15" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41524</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41535</v>
       </c>
       <c r="C16" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41614</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41626</v>
       </c>
       <c r="C17" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41705</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41717</v>
       </c>
       <c r="C18" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41803</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41823</v>
       </c>
       <c r="C19" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41887</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41900</v>
       </c>
       <c r="C20" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41978</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41990</v>
       </c>
       <c r="C21" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42081</v>
       </c>
       <c r="C22" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42167</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42191</v>
       </c>
       <c r="C23" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42258</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42270</v>
       </c>
       <c r="C24" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42347</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="C25" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42440</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42452</v>
       </c>
       <c r="C26" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42534</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="C27" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42622</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42634</v>
       </c>
       <c r="C28" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42717</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42724</v>
       </c>
       <c r="C29" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42808</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42815</v>
       </c>
       <c r="C30" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42895</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42915</v>
       </c>
       <c r="C31" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42991</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42998</v>
       </c>
       <c r="C32" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43080</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43089</v>
       </c>
       <c r="C33" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43171</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43180</v>
       </c>
       <c r="C34" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43258</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="C35" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43353</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43361</v>
       </c>
       <c r="C36" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43441</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43453</v>
       </c>
       <c r="C37" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43535</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43544</v>
       </c>
       <c r="C38" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43626</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="C39" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43718</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43726</v>
       </c>
       <c r="C40" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43809</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43817</v>
       </c>
       <c r="C41" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43900</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="C42" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43997</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44014</v>
       </c>
       <c r="C43" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44089</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44097</v>
       </c>
       <c r="C44" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44175</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="C45" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44270</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="C46" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44362</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="C47" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44453</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44461</v>
       </c>
       <c r="C48" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44544</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44551</v>
       </c>
       <c r="C49" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44634</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="C50" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44727</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="C51" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44818</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44825</v>
       </c>
       <c r="C52" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44908</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44915</v>
       </c>
       <c r="C53" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44998</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="C54" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45091</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45105</v>
       </c>
       <c r="C55" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45182</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45189</v>
       </c>
       <c r="C56" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45273</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="C57" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45364</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="C58" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45453</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="C59" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45546</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="C60" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45637</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45644</v>
       </c>
       <c r="C61" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45728</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45735</v>
       </c>
       <c r="C62" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45817</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45834</v>
       </c>
       <c r="C63" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45910</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45917</v>
       </c>
       <c r="C64" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46001</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="C65" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46092</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="C66" t="n">
@@ -12787,10 +12799,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46188</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="C67" t="n">
@@ -12819,10 +12831,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46281</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="C68" t="n">
@@ -12869,12 +12881,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GIS.xlsx
+++ b/salidas/empresas/GIS.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.1990327835083</v>
+        <v>12.19903373718262</v>
       </c>
       <c r="C2" t="n">
         <v>24.30500030517578</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.35964775085449</v>
+        <v>12.35964488983154</v>
       </c>
       <c r="C3" t="n">
         <v>24.625</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.71851634979248</v>
+        <v>12.71851062774658</v>
       </c>
       <c r="C4" t="n">
         <v>25.34000015258789</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.46572589874268</v>
+        <v>12.46572399139404</v>
       </c>
       <c r="C5" t="n">
         <v>24.67000007629395</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>13.1099853515625</v>
+        <v>13.10998916625977</v>
       </c>
       <c r="C6" t="n">
         <v>25.94499969482422</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.05187892913818</v>
+        <v>13.05187225341797</v>
       </c>
       <c r="C7" t="n">
         <v>25.82999992370605</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.20145034790039</v>
+        <v>13.20145416259766</v>
       </c>
       <c r="C8" t="n">
         <v>25.95000076293945</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7941198348999</v>
+        <v>13.79412174224854</v>
       </c>
       <c r="C9" t="n">
         <v>27.11499977111816</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.39695930480957</v>
+        <v>14.3969554901123</v>
       </c>
       <c r="C10" t="n">
         <v>28.29999923706055</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>14.54367542266846</v>
+        <v>14.54366302490234</v>
       </c>
       <c r="C11" t="n">
         <v>28.40999984741211</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.32099056243896</v>
+        <v>14.32098579406738</v>
       </c>
       <c r="C12" t="n">
         <v>27.97500038146973</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.74332523345947</v>
+        <v>14.74332237243652</v>
       </c>
       <c r="C13" t="n">
         <v>28.79999923706055</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.74695491790771</v>
+        <v>14.74695205688477</v>
       </c>
       <c r="C14" t="n">
         <v>28.6200008392334</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>15.52969360351562</v>
+        <v>15.52969837188721</v>
       </c>
       <c r="C17" t="n">
         <v>29.95000076293945</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>15.87710475921631</v>
+        <v>15.87711048126221</v>
       </c>
       <c r="C18" t="n">
         <v>30.6200008392334</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>15.14598560333252</v>
+        <v>15.1459903717041</v>
       </c>
       <c r="C19" t="n">
         <v>29.20999908447266</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.51664352416992</v>
+        <v>14.51663875579834</v>
       </c>
       <c r="C20" t="n">
         <v>27.80999946594238</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.58449935913086</v>
+        <v>14.58450508117676</v>
       </c>
       <c r="C21" t="n">
         <v>27.94000053405762</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>15.14042472839355</v>
+        <v>15.1404275894165</v>
       </c>
       <c r="C22" t="n">
         <v>29.0049991607666</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.17023658752441</v>
+        <v>15.17023277282715</v>
       </c>
       <c r="C23" t="n">
         <v>28.86499977111816</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.80616188049316</v>
+        <v>15.8061637878418</v>
       </c>
       <c r="C24" t="n">
         <v>30.07500076293945</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>14.97841453552246</v>
+        <v>14.97841167449951</v>
       </c>
       <c r="C25" t="n">
         <v>28.5</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>14.42571544647217</v>
+        <v>14.42571830749512</v>
       </c>
       <c r="C26" t="n">
         <v>27.26000022888184</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>14.81467247009277</v>
+        <v>14.81467628479004</v>
       </c>
       <c r="C27" t="n">
         <v>27.9950008392334</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.84394645690918</v>
+        <v>15.84394931793213</v>
       </c>
       <c r="C28" t="n">
         <v>29.94000053405762</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.08717918395996</v>
+        <v>16.0871753692627</v>
       </c>
       <c r="C29" t="n">
         <v>30.20000076293945</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.83293914794922</v>
+        <v>16.83294296264648</v>
       </c>
       <c r="C30" t="n">
         <v>31.60000038146973</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.18572425842285</v>
+        <v>16.18573188781738</v>
       </c>
       <c r="C31" t="n">
         <v>30.38500022888184</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.27105712890625</v>
+        <v>17.27106285095215</v>
       </c>
       <c r="C32" t="n">
         <v>32.19499969482422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.75118827819824</v>
+        <v>17.75119018554688</v>
       </c>
       <c r="C33" t="n">
         <v>33.09000015258789</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.43247604370117</v>
+        <v>18.43248176574707</v>
       </c>
       <c r="C34" t="n">
         <v>34.36000061035156</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>18.2869758605957</v>
+        <v>18.2869873046875</v>
       </c>
       <c r="C35" t="n">
         <v>33.86999893188477</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.05327606201172</v>
+        <v>17.05327796936035</v>
       </c>
       <c r="C36" t="n">
         <v>31.58499908447266</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.39998054504395</v>
+        <v>16.39997291564941</v>
       </c>
       <c r="C37" t="n">
         <v>30.375</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>16.08559799194336</v>
+        <v>16.0855884552002</v>
       </c>
       <c r="C38" t="n">
         <v>29.57500076293945</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.27170562744141</v>
+        <v>14.27171421051025</v>
       </c>
       <c r="C39" t="n">
         <v>26.23999977111816</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.56465816497803</v>
+        <v>13.56465244293213</v>
       </c>
       <c r="C40" t="n">
         <v>24.94000053405762</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>13.90259265899658</v>
+        <v>13.90258312225342</v>
       </c>
       <c r="C41" t="n">
         <v>25.34499931335449</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.03697776794434</v>
+        <v>14.03698348999023</v>
       </c>
       <c r="C42" t="n">
         <v>25.59000015258789</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.36442947387695</v>
+        <v>15.36442852020264</v>
       </c>
       <c r="C43" t="n">
         <v>28.01000022888184</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.28486061096191</v>
+        <v>16.28486251831055</v>
       </c>
       <c r="C44" t="n">
         <v>29.45499992370605</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>16.51154518127441</v>
+        <v>16.51154327392578</v>
       </c>
       <c r="C45" t="n">
         <v>29.86499977111816</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.79696273803711</v>
+        <v>17.79696464538574</v>
       </c>
       <c r="C46" t="n">
         <v>32.18999862670898</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>18.35560417175293</v>
+        <v>18.3556022644043</v>
       </c>
       <c r="C47" t="n">
         <v>32.95999908447266</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.93478584289551</v>
+        <v>18.93479156494141</v>
       </c>
       <c r="C48" t="n">
         <v>34</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.71724319458008</v>
+        <v>19.71723937988281</v>
       </c>
       <c r="C49" t="n">
         <v>35.40499877929688</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>19.99512481689453</v>
+        <v>19.9951343536377</v>
       </c>
       <c r="C50" t="n">
         <v>35.65499877929688</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.19140815734863</v>
+        <v>20.19140243530273</v>
       </c>
       <c r="C51" t="n">
         <v>36.00500106811523</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>19.84931373596191</v>
+        <v>19.84932708740234</v>
       </c>
       <c r="C52" t="n">
         <v>35.39500045776367</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>20.09346008300781</v>
+        <v>20.09346580505371</v>
       </c>
       <c r="C53" t="n">
         <v>35.58000183105469</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>20.11322784423828</v>
+        <v>20.11322593688965</v>
       </c>
       <c r="C54" t="n">
         <v>35.6150016784668</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>20.05957984924316</v>
+        <v>20.05957221984863</v>
       </c>
       <c r="C55" t="n">
         <v>35.52000045776367</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>21.53792190551758</v>
+        <v>21.53793334960938</v>
       </c>
       <c r="C59" t="n">
         <v>37.56000137329102</v>
@@ -1700,7 +1700,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.25917625427246</v>
+        <v>20.25917816162109</v>
       </c>
       <c r="C60" t="n">
         <v>35.33000183105469</v>
@@ -1729,7 +1729,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.40828132629395</v>
+        <v>20.40827178955078</v>
       </c>
       <c r="C61" t="n">
         <v>35.59000015258789</v>
@@ -1758,7 +1758,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.09746551513672</v>
+        <v>20.09745788574219</v>
       </c>
       <c r="C62" t="n">
         <v>34.77999877929688</v>
@@ -1787,7 +1787,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.46117210388184</v>
+        <v>21.46117782592773</v>
       </c>
       <c r="C63" t="n">
         <v>37.13999938964844</v>
@@ -1845,7 +1845,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>22.46576499938965</v>
+        <v>22.46575164794922</v>
       </c>
       <c r="C65" t="n">
         <v>38.58000183105469</v>
@@ -1874,7 +1874,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>23.15871810913086</v>
+        <v>23.15871429443359</v>
       </c>
       <c r="C66" t="n">
         <v>39.77000045776367</v>
@@ -1903,7 +1903,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.67380523681641</v>
+        <v>21.6738109588623</v>
       </c>
       <c r="C67" t="n">
         <v>37.22000122070312</v>
@@ -1932,7 +1932,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.92881774902344</v>
+        <v>21.92881202697754</v>
       </c>
       <c r="C68" t="n">
         <v>37.34999847412109</v>
@@ -1961,7 +1961,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.25759506225586</v>
+        <v>22.25760459899902</v>
       </c>
       <c r="C69" t="n">
         <v>37.90999984741211</v>
@@ -1990,7 +1990,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>22.5981388092041</v>
+        <v>22.59813499450684</v>
       </c>
       <c r="C70" t="n">
         <v>38.4900016784668</v>
@@ -2019,7 +2019,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.80446434020996</v>
+        <v>22.80446624755859</v>
       </c>
       <c r="C71" t="n">
         <v>38.52999877929688</v>
@@ -2042,7 +2042,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>23.64490699768066</v>
+        <v>23.6449089050293</v>
       </c>
       <c r="C72" t="n">
         <v>39.95000076293945</v>
@@ -2065,7 +2065,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>23.91715431213379</v>
+        <v>23.91716194152832</v>
       </c>
       <c r="C73" t="n">
         <v>40.40999984741211</v>
@@ -2123,7 +2123,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>22.84538078308105</v>
+        <v>22.84535980224609</v>
       </c>
       <c r="C75" t="n">
         <v>38.31000137329102</v>
@@ -2152,7 +2152,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.52518463134766</v>
+        <v>23.52517127990723</v>
       </c>
       <c r="C76" t="n">
         <v>39.45000076293945</v>
@@ -2181,7 +2181,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.3708324432373</v>
+        <v>23.37082862854004</v>
       </c>
       <c r="C77" t="n">
         <v>38.88999938964844</v>
@@ -2210,7 +2210,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.00425148010254</v>
+        <v>23.0042552947998</v>
       </c>
       <c r="C78" t="n">
         <v>38.27999877929688</v>
@@ -2239,7 +2239,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>23.16049957275391</v>
+        <v>23.16049194335938</v>
       </c>
       <c r="C79" t="n">
         <v>38.54000091552734</v>
@@ -2326,7 +2326,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.15188789367676</v>
+        <v>24.15189170837402</v>
       </c>
       <c r="C82" t="n">
         <v>39.84999847412109</v>
@@ -2355,7 +2355,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.49175071716309</v>
+        <v>24.49174499511719</v>
       </c>
       <c r="C83" t="n">
         <v>40.08000183105469</v>
@@ -2384,7 +2384,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.04781913757324</v>
+        <v>25.04781723022461</v>
       </c>
       <c r="C84" t="n">
         <v>40.9900016784668</v>
@@ -2413,7 +2413,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>24.69950675964355</v>
+        <v>24.69951248168945</v>
       </c>
       <c r="C85" t="n">
         <v>40.41999816894531</v>
@@ -2442,7 +2442,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>25.83326530456543</v>
+        <v>25.8332576751709</v>
       </c>
       <c r="C86" t="n">
         <v>41.93999862670898</v>
@@ -2471,7 +2471,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.4880313873291</v>
+        <v>28.48803520202637</v>
       </c>
       <c r="C87" t="n">
         <v>46.25</v>
@@ -2500,7 +2500,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>30.37286376953125</v>
+        <v>30.37287139892578</v>
       </c>
       <c r="C88" t="n">
         <v>49.31000137329102</v>
@@ -2529,7 +2529,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>31.2682991027832</v>
+        <v>31.26829528808594</v>
       </c>
       <c r="C89" t="n">
         <v>50.41999816894531</v>
@@ -2558,7 +2558,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>29.19696807861328</v>
+        <v>29.19696617126465</v>
       </c>
       <c r="C90" t="n">
         <v>47.08000183105469</v>
@@ -2587,7 +2587,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>30.09618759155273</v>
+        <v>30.09618949890137</v>
       </c>
       <c r="C91" t="n">
         <v>48.52999877929688</v>
@@ -2645,7 +2645,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>30.82502555847168</v>
+        <v>30.82501411437988</v>
       </c>
       <c r="C93" t="n">
         <v>49.31999969482422</v>
@@ -2703,7 +2703,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>31.76404190063477</v>
+        <v>31.7640323638916</v>
       </c>
       <c r="C95" t="n">
         <v>50.41999816894531</v>
@@ -2732,7 +2732,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.77034568786621</v>
+        <v>31.77033805847168</v>
       </c>
       <c r="C96" t="n">
         <v>50.43000030517578</v>
@@ -2761,7 +2761,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.44275283813477</v>
+        <v>31.44274139404297</v>
       </c>
       <c r="C97" t="n">
         <v>49.90999984741211</v>
@@ -2790,7 +2790,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.48445129394531</v>
+        <v>30.48445892333984</v>
       </c>
       <c r="C98" t="n">
         <v>48.02000045776367</v>
@@ -2819,7 +2819,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.76044464111328</v>
+        <v>31.76044273376465</v>
       </c>
       <c r="C99" t="n">
         <v>50.02999877929688</v>
@@ -2848,7 +2848,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>32.89679718017578</v>
+        <v>32.89678955078125</v>
       </c>
       <c r="C100" t="n">
         <v>51.81999969482422</v>
@@ -2877,7 +2877,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.92686080932617</v>
+        <v>33.92685699462891</v>
       </c>
       <c r="C101" t="n">
         <v>53.02000045776367</v>
@@ -2906,7 +2906,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>35.14905166625977</v>
+        <v>35.14905548095703</v>
       </c>
       <c r="C102" t="n">
         <v>54.93000030517578</v>
@@ -2935,7 +2935,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.61972427368164</v>
+        <v>33.61972045898438</v>
       </c>
       <c r="C103" t="n">
         <v>52.54000091552734</v>
@@ -2964,7 +2964,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>32.33860397338867</v>
+        <v>32.33858489990234</v>
       </c>
       <c r="C104" t="n">
         <v>50.15000152587891</v>
@@ -2993,7 +2993,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>34.42140579223633</v>
+        <v>34.42140960693359</v>
       </c>
       <c r="C105" t="n">
         <v>53.38000106811523</v>
@@ -3051,7 +3051,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>33.78176116943359</v>
+        <v>33.78175354003906</v>
       </c>
       <c r="C107" t="n">
         <v>51.95999908447266</v>
@@ -3080,7 +3080,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>34.29538345336914</v>
+        <v>34.29536819458008</v>
       </c>
       <c r="C108" t="n">
         <v>52.75</v>
@@ -3109,7 +3109,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>34.67246627807617</v>
+        <v>34.67245483398438</v>
       </c>
       <c r="C109" t="n">
         <v>53.33000183105469</v>
@@ -3138,7 +3138,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>34.38522720336914</v>
+        <v>34.38523483276367</v>
       </c>
       <c r="C110" t="n">
         <v>52.47999954223633</v>
@@ -3167,7 +3167,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>35.24354934692383</v>
+        <v>35.24355316162109</v>
       </c>
       <c r="C111" t="n">
         <v>53.79000091552734</v>
@@ -3196,7 +3196,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>37.08468627929688</v>
+        <v>37.08467864990234</v>
       </c>
       <c r="C112" t="n">
         <v>56.59999847412109</v>
@@ -3254,7 +3254,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>37.08076477050781</v>
+        <v>37.08077621459961</v>
       </c>
       <c r="C114" t="n">
         <v>56.15000152587891</v>
@@ -3283,7 +3283,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>36.79681396484375</v>
+        <v>36.79680633544922</v>
       </c>
       <c r="C115" t="n">
         <v>55.72000122070312</v>
@@ -3312,7 +3312,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>38.73558807373047</v>
+        <v>38.73558044433594</v>
       </c>
       <c r="C116" t="n">
         <v>58.20999908447266</v>
@@ -3341,7 +3341,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>37.77069473266602</v>
+        <v>37.77067565917969</v>
       </c>
       <c r="C117" t="n">
         <v>56.7599983215332</v>
@@ -3399,7 +3399,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.97693252563477</v>
+        <v>38.9769401550293</v>
       </c>
       <c r="C119" t="n">
         <v>58.11000061035156</v>
@@ -3428,7 +3428,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>38.7421760559082</v>
+        <v>38.74218368530273</v>
       </c>
       <c r="C120" t="n">
         <v>57.7599983215332</v>
@@ -3486,7 +3486,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>38.20002365112305</v>
+        <v>38.20003128051758</v>
       </c>
       <c r="C122" t="n">
         <v>56.5099983215332</v>
@@ -3515,7 +3515,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>39.78183746337891</v>
+        <v>39.78184509277344</v>
       </c>
       <c r="C123" t="n">
         <v>58.84999847412109</v>
@@ -3544,7 +3544,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>42.82377624511719</v>
+        <v>42.82378005981445</v>
       </c>
       <c r="C124" t="n">
         <v>63.34999847412109</v>
@@ -3573,7 +3573,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>41.76456832885742</v>
+        <v>41.76457214355469</v>
       </c>
       <c r="C125" t="n">
         <v>61.34000015258789</v>
@@ -3602,7 +3602,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>42.74502944946289</v>
+        <v>42.74503326416016</v>
       </c>
       <c r="C126" t="n">
         <v>62.77999877929688</v>
@@ -3631,7 +3631,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>48.55964279174805</v>
+        <v>48.55966567993164</v>
       </c>
       <c r="C127" t="n">
         <v>71.31999969482422</v>
@@ -3660,7 +3660,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>49.27370452880859</v>
+        <v>49.27370834350586</v>
       </c>
       <c r="C128" t="n">
         <v>71.88999938964844</v>
@@ -3689,7 +3689,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>48.54033660888672</v>
+        <v>48.54031753540039</v>
       </c>
       <c r="C129" t="n">
         <v>70.81999969482422</v>
@@ -3718,7 +3718,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>43.78361511230469</v>
+        <v>43.78362274169922</v>
       </c>
       <c r="C130" t="n">
         <v>63.88000106811523</v>
@@ -3747,7 +3747,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>42.80724334716797</v>
+        <v>42.80723571777344</v>
       </c>
       <c r="C131" t="n">
         <v>61.97999954223633</v>
@@ -3776,7 +3776,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>42.08897018432617</v>
+        <v>42.08896255493164</v>
       </c>
       <c r="C132" t="n">
         <v>60.93999862670898</v>
@@ -3805,7 +3805,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>42.66220474243164</v>
+        <v>42.66221237182617</v>
       </c>
       <c r="C133" t="n">
         <v>61.77000045776367</v>
@@ -3834,7 +3834,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>43.48789978027344</v>
+        <v>43.4879035949707</v>
       </c>
       <c r="C134" t="n">
         <v>62.47999954223633</v>
@@ -3863,7 +3863,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>42.019287109375</v>
+        <v>42.01927947998047</v>
       </c>
       <c r="C135" t="n">
         <v>60.36999893188477</v>
@@ -3892,7 +3892,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>41.07267379760742</v>
+        <v>41.07267761230469</v>
       </c>
       <c r="C136" t="n">
         <v>59.0099983215332</v>
@@ -3921,7 +3921,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>40.36122512817383</v>
+        <v>40.36122131347656</v>
       </c>
       <c r="C137" t="n">
         <v>57.5099983215332</v>
@@ -3950,7 +3950,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>39.82083129882812</v>
+        <v>39.82083892822266</v>
       </c>
       <c r="C138" t="n">
         <v>56.7400016784668</v>
@@ -3979,7 +3979,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>38.88040542602539</v>
+        <v>38.88040924072266</v>
       </c>
       <c r="C139" t="n">
         <v>55.40000152587891</v>
@@ -4037,7 +4037,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>37.71570587158203</v>
+        <v>37.71569442749023</v>
       </c>
       <c r="C141" t="n">
         <v>53.2599983215332</v>
@@ -4124,7 +4124,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>40.43291473388672</v>
+        <v>40.43292617797852</v>
       </c>
       <c r="C144" t="n">
         <v>56.56000137329102</v>
@@ -4211,7 +4211,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.43352127075195</v>
+        <v>36.43351364135742</v>
       </c>
       <c r="C147" t="n">
         <v>50.54999923706055</v>
@@ -4240,7 +4240,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.47663116455078</v>
+        <v>32.47663497924805</v>
       </c>
       <c r="C148" t="n">
         <v>45.06000137329102</v>
@@ -4269,7 +4269,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>31.86867904663086</v>
+        <v>31.86868476867676</v>
       </c>
       <c r="C149" t="n">
         <v>43.7400016784668</v>
@@ -4298,7 +4298,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>30.81222915649414</v>
+        <v>30.81222534179688</v>
       </c>
       <c r="C150" t="n">
         <v>42.29000091552734</v>
@@ -4327,7 +4327,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>32.24755477905273</v>
+        <v>32.2475471496582</v>
       </c>
       <c r="C151" t="n">
         <v>44.2599983215332</v>
@@ -4356,7 +4356,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>33.92813873291016</v>
+        <v>33.92814254760742</v>
       </c>
       <c r="C152" t="n">
         <v>46.06000137329102</v>
@@ -4385,7 +4385,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>33.89130783081055</v>
+        <v>33.89130401611328</v>
       </c>
       <c r="C153" t="n">
         <v>46.0099983215332</v>
@@ -4414,7 +4414,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>31.61519241333008</v>
+        <v>31.61519050598145</v>
       </c>
       <c r="C154" t="n">
         <v>42.91999816894531</v>
@@ -4443,7 +4443,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>32.6235237121582</v>
+        <v>32.62351608276367</v>
       </c>
       <c r="C155" t="n">
         <v>43.79999923706055</v>
@@ -4472,7 +4472,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>31.51371955871582</v>
+        <v>31.51372146606445</v>
       </c>
       <c r="C156" t="n">
         <v>42.31000137329102</v>
@@ -4501,7 +4501,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.00364685058594</v>
+        <v>29.0036506652832</v>
       </c>
       <c r="C157" t="n">
         <v>38.93999862670898</v>
@@ -4530,7 +4530,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>33.49970245361328</v>
+        <v>33.49969482421875</v>
       </c>
       <c r="C158" t="n">
         <v>44.43999862670898</v>
@@ -4559,7 +4559,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.52746200561523</v>
+        <v>35.5274658203125</v>
       </c>
       <c r="C159" t="n">
         <v>47.13000106811523</v>
@@ -4588,7 +4588,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>39.01010131835938</v>
+        <v>39.01010513305664</v>
       </c>
       <c r="C160" t="n">
         <v>51.75</v>
@@ -4617,7 +4617,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.17314147949219</v>
+        <v>39.17313766479492</v>
       </c>
       <c r="C161" t="n">
         <v>51.47000122070312</v>
@@ -4646,7 +4646,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>37.62813186645508</v>
+        <v>37.62812805175781</v>
       </c>
       <c r="C162" t="n">
         <v>49.43999862670898</v>
@@ -4675,7 +4675,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.97227478027344</v>
+        <v>39.97226333618164</v>
       </c>
       <c r="C163" t="n">
         <v>52.52000045776367</v>
@@ -4704,7 +4704,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>40.79111099243164</v>
+        <v>40.79111862182617</v>
       </c>
       <c r="C164" t="n">
         <v>53.11000061035156</v>
@@ -4733,7 +4733,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>41.32107162475586</v>
+        <v>41.32107543945312</v>
       </c>
       <c r="C165" t="n">
         <v>53.79999923706055</v>
@@ -4762,7 +4762,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>42.33489608764648</v>
+        <v>42.33489227294922</v>
       </c>
       <c r="C166" t="n">
         <v>55.11999893188477</v>
@@ -4791,7 +4791,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>39.41970443725586</v>
+        <v>39.41971969604492</v>
       </c>
       <c r="C167" t="n">
         <v>50.86000061035156</v>
@@ -4849,7 +4849,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.51238250732422</v>
+        <v>41.51237106323242</v>
       </c>
       <c r="C169" t="n">
         <v>53.56000137329102</v>
@@ -4907,7 +4907,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.33261489868164</v>
+        <v>38.33262252807617</v>
       </c>
       <c r="C171" t="n">
         <v>49</v>
@@ -4936,7 +4936,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>41.28189468383789</v>
+        <v>41.28189849853516</v>
       </c>
       <c r="C172" t="n">
         <v>52.77000045776367</v>
@@ -4965,7 +4965,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>47.26216888427734</v>
+        <v>47.26217269897461</v>
       </c>
       <c r="C173" t="n">
         <v>59.88999938964844</v>
@@ -4994,7 +4994,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>49.74799346923828</v>
+        <v>49.74800491333008</v>
       </c>
       <c r="C174" t="n">
         <v>63.04000091552734</v>
@@ -5023,7 +5023,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>48.65107345581055</v>
+        <v>48.65108108520508</v>
       </c>
       <c r="C175" t="n">
         <v>61.65000152587891</v>
@@ -5052,7 +5052,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>50.32126998901367</v>
+        <v>50.32126235961914</v>
       </c>
       <c r="C176" t="n">
         <v>63.27000045776367</v>
@@ -5081,7 +5081,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>50.86209869384766</v>
+        <v>50.86209487915039</v>
       </c>
       <c r="C177" t="n">
         <v>63.95000076293945</v>
@@ -5110,7 +5110,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>49.05667114257812</v>
+        <v>49.05667495727539</v>
       </c>
       <c r="C178" t="n">
         <v>61.68000030517578</v>
@@ -5168,7 +5168,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>48.77657699584961</v>
+        <v>48.77657318115234</v>
       </c>
       <c r="C180" t="n">
         <v>60.81999969482422</v>
@@ -5226,7 +5226,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>47.00188446044922</v>
+        <v>47.00187683105469</v>
       </c>
       <c r="C182" t="n">
         <v>58.09999847412109</v>
@@ -5284,7 +5284,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>49.60680770874023</v>
+        <v>49.60680389404297</v>
       </c>
       <c r="C184" t="n">
         <v>61.31999969482422</v>
@@ -5313,7 +5313,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>49.64711761474609</v>
+        <v>49.64711380004883</v>
       </c>
       <c r="C185" t="n">
         <v>60.86000061035156</v>
@@ -5342,7 +5342,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>51.27863311767578</v>
+        <v>51.27862930297852</v>
       </c>
       <c r="C186" t="n">
         <v>62.86000061035156</v>
@@ -5371,7 +5371,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>49.7042236328125</v>
+        <v>49.70421981811523</v>
       </c>
       <c r="C187" t="n">
         <v>60.93000030517578</v>
@@ -5458,7 +5458,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>49.2143440246582</v>
+        <v>49.21434020996094</v>
       </c>
       <c r="C190" t="n">
         <v>59.81999969482422</v>
@@ -5516,7 +5516,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>51.23921966552734</v>
+        <v>51.23922348022461</v>
       </c>
       <c r="C192" t="n">
         <v>61.77000045776367</v>
@@ -5545,7 +5545,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>55.89280700683594</v>
+        <v>55.89280319213867</v>
       </c>
       <c r="C193" t="n">
         <v>67.37999725341797</v>
@@ -5574,7 +5574,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>57.39859771728516</v>
+        <v>57.39859390258789</v>
       </c>
       <c r="C194" t="n">
         <v>68.68000030517578</v>
@@ -5632,7 +5632,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>56.59628677368164</v>
+        <v>56.59628295898438</v>
       </c>
       <c r="C196" t="n">
         <v>67.72000122070312</v>
@@ -5661,7 +5661,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>59.54740142822266</v>
+        <v>59.54738998413086</v>
       </c>
       <c r="C197" t="n">
         <v>70.73000335693359</v>
@@ -5719,7 +5719,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>63.52113342285156</v>
+        <v>63.52112579345703</v>
       </c>
       <c r="C199" t="n">
         <v>75.44999694824219</v>
@@ -5748,7 +5748,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>63.41476821899414</v>
+        <v>63.41476440429688</v>
       </c>
       <c r="C200" t="n">
         <v>74.79000091552734</v>
@@ -5806,7 +5806,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>64.95795440673828</v>
+        <v>64.95794677734375</v>
       </c>
       <c r="C202" t="n">
         <v>76.61000061035156</v>
@@ -5864,7 +5864,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>72.83248138427734</v>
+        <v>72.83247375488281</v>
       </c>
       <c r="C204" t="n">
         <v>85.30000305175781</v>
@@ -5893,7 +5893,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>71.59441375732422</v>
+        <v>71.59439849853516</v>
       </c>
       <c r="C205" t="n">
         <v>83.84999847412109</v>
@@ -5922,7 +5922,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>67.32978820800781</v>
+        <v>67.32979583740234</v>
       </c>
       <c r="C206" t="n">
         <v>78.36000061035156</v>
@@ -5980,7 +5980,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>73.43036651611328</v>
+        <v>73.43037414550781</v>
       </c>
       <c r="C208" t="n">
         <v>85.45999908447266</v>
@@ -6009,7 +6009,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>76.62946319580078</v>
+        <v>76.62945556640625</v>
       </c>
       <c r="C209" t="n">
         <v>88.62999725341797</v>
@@ -6038,7 +6038,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>72.76470947265625</v>
+        <v>72.76470184326172</v>
       </c>
       <c r="C210" t="n">
         <v>84.16000366210938</v>
@@ -6067,7 +6067,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>66.31478118896484</v>
+        <v>66.31480407714844</v>
       </c>
       <c r="C211" t="n">
         <v>76.69999694824219</v>
@@ -6096,7 +6096,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>65.12287902832031</v>
+        <v>65.12288665771484</v>
       </c>
       <c r="C212" t="n">
         <v>74.73999786376953</v>
@@ -6125,7 +6125,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>58.95390319824219</v>
+        <v>58.95389175415039</v>
       </c>
       <c r="C213" t="n">
         <v>67.66000366210938</v>
@@ -6212,7 +6212,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>55.9984016418457</v>
+        <v>55.99840545654297</v>
       </c>
       <c r="C216" t="n">
         <v>63.65999984741211</v>
@@ -6241,7 +6241,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>57.30027389526367</v>
+        <v>57.3002815246582</v>
       </c>
       <c r="C217" t="n">
         <v>65.13999938964844</v>
@@ -6270,7 +6270,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>57.62392807006836</v>
+        <v>57.62393569946289</v>
       </c>
       <c r="C218" t="n">
         <v>64.91000366210938</v>
@@ -6299,7 +6299,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>56.97586441040039</v>
+        <v>56.97587203979492</v>
       </c>
       <c r="C219" t="n">
         <v>64.18000030517578</v>
@@ -6328,7 +6328,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>62.1159553527832</v>
+        <v>62.11594009399414</v>
       </c>
       <c r="C220" t="n">
         <v>69.97000122070312</v>
@@ -6357,7 +6357,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>63.08263778686523</v>
+        <v>63.08264541625977</v>
       </c>
       <c r="C221" t="n">
         <v>70.45999908447266</v>
@@ -6386,7 +6386,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>61.55168533325195</v>
+        <v>61.55168151855469</v>
       </c>
       <c r="C222" t="n">
         <v>68.75</v>
@@ -6415,7 +6415,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>56.63650512695312</v>
+        <v>56.63650131225586</v>
       </c>
       <c r="C223" t="n">
         <v>63.2599983215332</v>
@@ -6444,7 +6444,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>60.69112014770508</v>
+        <v>60.69112777709961</v>
       </c>
       <c r="C224" t="n">
         <v>67.13999938964844</v>
@@ -6502,7 +6502,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>66.75661468505859</v>
+        <v>66.75662231445312</v>
       </c>
       <c r="C226" t="n">
         <v>73.84999847412109</v>
@@ -6531,7 +6531,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>62.00278854370117</v>
+        <v>62.00279235839844</v>
       </c>
       <c r="C227" t="n">
         <v>68.01999664306641</v>
@@ -6560,7 +6560,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>60.39848709106445</v>
+        <v>60.39848327636719</v>
       </c>
       <c r="C228" t="n">
         <v>66.26000213623047</v>
@@ -6589,7 +6589,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>58.12875366210938</v>
+        <v>58.12874984741211</v>
       </c>
       <c r="C229" t="n">
         <v>63.77000045776367</v>
@@ -6618,7 +6618,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>55.36470794677734</v>
+        <v>55.36471176147461</v>
       </c>
       <c r="C230" t="n">
         <v>60.13999938964844</v>
@@ -6676,7 +6676,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>55.04249954223633</v>
+        <v>55.04250335693359</v>
       </c>
       <c r="C232" t="n">
         <v>59.79000091552734</v>
